--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M2B8_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M2B8_IN_Piura.xlsx
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>7.67</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>37.9</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C13" s="30">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>46.9</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>7.52</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>116.099</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>8.9254</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>7.69</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1960,11 +1960,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>107.1736</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>92.31</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2139,11 +2139,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>116.1362</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2262,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2346,6 +2347,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2390,6 +2392,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="144" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2716,11 +2719,11 @@
       </c>
       <c r="B15" s="32">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>1773.19</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2730,19 +2733,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>17.0</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.3616</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>7.27</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>97.11</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
